--- a/Coupang_Top20_20260807.xlsx
+++ b/Coupang_Top20_20260807.xlsx
@@ -448,84 +448,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>알리사 100단 아이스 터보 MAX 휴대용 선풍기</t>
+          <t>신지모루 IPX8스펀지 튜브 4중잠금 스마트폰 방수팩+ 크로스 스트랩 + 암밴드 + 핸드 스트랩</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28380</v>
+        <v>9900</v>
       </c>
       <c r="C2">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8719219704&amp;itemId=25325956860&amp;vendorItemId=92859054401&amp;traceid=V0-113-3390c08a48f3cae9", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7342693694&amp;itemId=18876369675&amp;vendorItemId=86004954806&amp;traceid=V0-113-4a6c0db477492449", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>신지모루 IPX8스펀지 튜브 4중잠금 스마트폰 방수팩+ 크로스 스트랩 + 암밴드 + 핸드 스트랩</t>
+          <t>아이젠트 에어컨 실외기 8중 난연 과열 방지 열 차단 절전 커버 T 9mm</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9900</v>
+        <v>9500</v>
       </c>
       <c r="C3">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7342693694&amp;itemId=18876369675&amp;vendorItemId=86004954806&amp;traceid=V0-113-4a6c0db477492449", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9659928977&amp;itemId=28877589942&amp;vendorItemId=95871861980&amp;traceid=V0-113-cf7125ae90b0eab8", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Apple 2025 에어팟 프로 3 USB-C 블루투스 이어폰</t>
+          <t>아이리버 25W 2포트 초고속 가정용 충전기 + CtoC 케이블 세트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>329890</v>
+        <v>8800</v>
       </c>
       <c r="C4">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9024163013&amp;itemId=26462308675&amp;vendorItemId=93437588392&amp;traceid=V0-113-848acafd9e852dbc", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8939019740&amp;itemId=26138373322&amp;vendorItemId=93118512226&amp;traceid=V0-113-fd1e07a2d9481cd8", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>아이리버 25W 2포트 초고속 가정용 충전기 + CtoC 케이블 세트</t>
+          <t>홈플래닛 발터치 리모컨 스탠드형 선풍기</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8800</v>
+        <v>29690</v>
       </c>
       <c r="C5">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8939019740&amp;itemId=26138373322&amp;vendorItemId=93118512226&amp;traceid=V0-113-fd1e07a2d9481cd8", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1459643219&amp;itemId=2511597502&amp;vendorItemId=92134731921&amp;traceid=V0-113-62386184a6cb7f37", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>아이젠트 에어컨 실외기 8중 난연 과열 방지 열 차단 절전 커버 T 9mm</t>
+          <t>신지모루 C to C PD 고속충전 케이블 60W</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7940</v>
+        <v>6900</v>
       </c>
       <c r="C6">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9659928977&amp;itemId=28877589942&amp;vendorItemId=80844234213&amp;traceid=V0-113-cf7125ae90b0eab8", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9344838202&amp;itemId=13761827932&amp;vendorItemId=81012487257&amp;traceid=V0-113-0a9564caf484529f", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신지모루 C to C PD 고속충전 케이블 60W</t>
+          <t>New 대형냉각패드 위니쿨 급속냉각 휴대용 목 넥 선풍기 BLDC 대용량5200mAh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6100</v>
+        <v>51600</v>
       </c>
       <c r="C7">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9344838202&amp;itemId=13761827932&amp;vendorItemId=81012487257&amp;traceid=V0-113-0a9564caf484529f", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9530983694&amp;itemId=28422964479&amp;vendorItemId=90727418152&amp;traceid=V0-113-b2175c2d8d40ede3", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
@@ -546,182 +546,182 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>New 대형냉각패드 위니쿨 급속냉각 휴대용 목 넥 선풍기 BLDC 대용량5200mAh</t>
+          <t>신지모루 오피디 25W GaN 듀얼포트 PPS 초고속 PD 충전기</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51600</v>
+        <v>8980</v>
       </c>
       <c r="C9">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9530983694&amp;itemId=28422964479&amp;vendorItemId=90727418152&amp;traceid=V0-113-b2175c2d8d40ede3", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7415163807&amp;itemId=19222022188&amp;vendorItemId=86338760049&amp;traceid=V0-113-693c11efc2bbce39", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>신지모루 오피디 25W GaN 듀얼포트 PPS 초고속 PD 충전기</t>
+          <t>한경희생활과학 초미세풍 발터치 리모컨 선풍기</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8980</v>
+        <v>39890</v>
       </c>
       <c r="C10">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7415163807&amp;itemId=19222022188&amp;vendorItemId=86338760049&amp;traceid=V0-113-693c11efc2bbce39", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8049298764&amp;itemId=22568615219&amp;vendorItemId=89610481080&amp;traceid=V0-113-c6225c8b32161464", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>로지텍 2세대 LIGHTSYNC 게이밍 유선마우스</t>
+          <t>쿠쿠 전자레인지 다이얼식 20L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23390</v>
+        <v>59900</v>
       </c>
       <c r="C11">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9595729489&amp;itemId=28645359064&amp;vendorItemId=71308308451&amp;traceid=V0-113-4437218efaa33548", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6784715012&amp;itemId=15967393537&amp;vendorItemId=5493101444&amp;traceid=V0-113-70e181a43b411328", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>쿠쿠 전자레인지 다이얼식 20L</t>
+          <t>지파워 PD25W C타입 초고속 충전기 + 케이블 세트</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59890</v>
+        <v>12900</v>
       </c>
       <c r="C12">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6784715012&amp;itemId=15967393537&amp;vendorItemId=5493101444&amp;traceid=V0-113-70e181a43b411328", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8412528497&amp;itemId=27550736330&amp;vendorItemId=91340765355&amp;traceid=V0-113-ed33d597ead95ac8", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UOOFON 목 선풍기 100단 파워풍량 4000mAh 냉감패드 내장 슬롯 트위스트 무선 휴대용 선풍기</t>
+          <t>로지텍 2세대 LIGHTSYNC 게이밍 유선마우스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19900</v>
+        <v>23010</v>
       </c>
       <c r="C13">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9457219527&amp;itemId=28139005803&amp;vendorItemId=95670322147&amp;traceid=V0-113-bd193067327341e8", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9595729489&amp;itemId=28645359064&amp;vendorItemId=71308308451&amp;traceid=V0-113-4437218efaa33548", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>루메나 선풍기 무선 탁상용</t>
+          <t>코멧 에어컨 실외기 8중 난연 과열 방지 열 차단 절전 커버 T 9mm 국내생산</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36900</v>
+        <v>7490</v>
       </c>
       <c r="C14">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9041217547&amp;itemId=22524207601&amp;vendorItemId=89545588602&amp;traceid=V0-113-93af8ab0ce6bd264", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1765604934&amp;itemId=3006422721&amp;vendorItemId=70994645165&amp;traceid=V0-113-189af88545482d4a", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>코멧 에어컨 실외기 8중 난연 과열 방지 열 차단 절전 커버 T 9mm 국내생산</t>
+          <t>UOOFON 목 선풍기 100단 파워풍량 4000mAh 냉감패드 내장 슬롯 트위스트 무선 휴대용 선풍기</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7390</v>
+        <v>19900</v>
       </c>
       <c r="C15">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1765604934&amp;itemId=3006422721&amp;vendorItemId=70994645165&amp;traceid=V0-113-189af88545482d4a", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9457219527&amp;itemId=28139005803&amp;vendorItemId=95670322147&amp;traceid=V0-113-bd193067327341e8", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>맥스틸 애플 아이폰 삼성 갤럭시 호환 C타입 오픈형 유선 이어폰, GM-EC20, 화이트</t>
+          <t>팬톤 PD 22.5W 초고속충전 대용량 케이블 일체형 미러 보조배터리 10000mAh PGB-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4690</v>
+        <v>18900</v>
       </c>
       <c r="C16">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8371538377&amp;itemId=24191384321&amp;vendorItemId=91477513891&amp;traceid=V0-113-3296e603157fd219", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7925483056&amp;itemId=21787007376&amp;vendorItemId=88835705816&amp;traceid=V0-113-f89728f61fd6871b", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>신일 스탠드형 선풍기 30cm(12인치)</t>
+          <t>[kc 인증] 미니 냉풍기 저소음 대풍량 사무실/수면/캠핑 야외 미니냉풍기</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48200</v>
+        <v>11900</v>
       </c>
       <c r="C17">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7249246657&amp;itemId=18436391484&amp;vendorItemId=85577711276&amp;traceid=V0-113-7ecbd6c6a0b54bdb", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7348510314&amp;itemId=28542853825&amp;vendorItemId=95796718932&amp;traceid=V0-113-fb55c3b0bfa8856d", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>라우드 파스텔 핸드폰 방수팩 1+1 물놀이 방수케이스</t>
+          <t>루메나 선풍기 무선 탁상용</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7480</v>
+        <v>37900</v>
       </c>
       <c r="C18">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8579465515&amp;itemId=24866105589&amp;vendorItemId=91873096417&amp;traceid=V0-113-0578ccd639e04351", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9041217547&amp;itemId=22524207601&amp;vendorItemId=89545588602&amp;traceid=V0-113-93af8ab0ce6bd264", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[kc 인증] 미니 냉풍기 저소음 대풍량 사무실/수면/캠핑 야외 미니냉풍기</t>
+          <t>신일 스탠드형 선풍기 30cm(12인치)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11900</v>
+        <v>48200</v>
       </c>
       <c r="C19">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7348510314&amp;itemId=28542853825&amp;vendorItemId=95796718932&amp;traceid=V0-113-fb55c3b0bfa8856d", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7249246657&amp;itemId=18436391484&amp;vendorItemId=85577711276&amp;traceid=V0-113-7ecbd6c6a0b54bdb", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>이츠라이프 C타입 PD to 라이트닝 8핀 18W 고속 충전 케이블</t>
+          <t>KONLI 노이즈 캔슬링 커널형 무선 블루투스 이어폰  방수</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5500</v>
+        <v>15900</v>
       </c>
       <c r="C20">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6344753372&amp;itemId=13325965156&amp;vendorItemId=80581901540&amp;traceid=V0-113-a0617e06ddc13702", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8082654809&amp;itemId=28798747378&amp;vendorItemId=95768196637&amp;traceid=V0-113-ccaa071f34b54039", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>홈플래닛 퀄컴 공식인증 QC3.0 18W고속충전기 + 타입C케이블 1.2m 세트</t>
+          <t>라우드 파스텔 핸드폰 방수팩 1+1 물놀이 방수케이스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6980</v>
+        <v>7480</v>
       </c>
       <c r="C21">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1628630781&amp;itemId=2778296479&amp;vendorItemId=89645323681&amp;traceid=V0-113-e16801aaf71b1d25", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8579465515&amp;itemId=24866105589&amp;vendorItemId=91873096417&amp;traceid=V0-113-0578ccd639e04351", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
